--- a/data/orders.xlsx
+++ b/data/orders.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +48,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,6 +461,11 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>镜片码</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -493,12 +498,17 @@
           <t>-0.50</t>
         </is>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="2" t="n">
         <v>46037</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>渐进镜</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>063CDFCC6436431B</t>
         </is>
       </c>
     </row>
@@ -533,10 +543,14 @@
           <t>-0.75</t>
         </is>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="2" t="n">
         <v>46042</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>A3DA83D2684B4E5A</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -569,12 +583,17 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>单光镜</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>520319E0218740B1</t>
         </is>
       </c>
     </row>
@@ -609,10 +628,14 @@
           <t>-1.25</t>
         </is>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="2" t="n">
         <v>46071</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>A637BC8C8C6E4ED2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -645,12 +668,17 @@
           <t>-0.50</t>
         </is>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>防蓝光</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4A9797EE57054CED</t>
         </is>
       </c>
     </row>

--- a/data/orders.xlsx
+++ b/data/orders.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="订单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -48,9 +48,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -498,7 +497,7 @@
           <t>-0.50</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="1" t="n">
         <v>46037</v>
       </c>
       <c r="H2" t="inlineStr">
@@ -508,7 +507,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>063CDFCC6436431B</t>
+          <t>B570892F162D4CF2</t>
         </is>
       </c>
     </row>
@@ -543,12 +542,12 @@
           <t>-0.75</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="1" t="n">
         <v>46042</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>A3DA83D2684B4E5A</t>
+          <t>1EF66E96D35B4FE4</t>
         </is>
       </c>
     </row>
@@ -583,7 +582,7 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="1" t="n">
         <v>46056</v>
       </c>
       <c r="H4" t="inlineStr">
@@ -593,7 +592,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>520319E0218740B1</t>
+          <t>18A9964DFD1643FA</t>
         </is>
       </c>
     </row>
@@ -610,30 +609,30 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-1.25</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>46071</v>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>46063</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>A637BC8C8C6E4ED2</t>
+          <t>E6D4AF4C563D4A0A</t>
         </is>
       </c>
     </row>
@@ -650,7 +649,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+2.50</t>
+          <t>+2.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -660,25 +659,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>+2.25</t>
+          <t>+1.75</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.50</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>防蓝光</t>
+          <t>双光镜</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4A9797EE57054CED</t>
+          <t>2FFF578D64F843F4</t>
         </is>
       </c>
     </row>
